--- a/docs/seguimiento/02_Backlogs_RAID_Decisiones_y_Cambios_Fase2.xlsx
+++ b/docs/seguimiento/02_Backlogs_RAID_Decisiones_y_Cambios_Fase2.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Backlog" sheetId="1" r:id="R32f32fe2e50f42b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint_Backlogs" sheetId="2" r:id="R9a9a2837d5ae4d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAID" sheetId="3" r:id="R876fb14bf5d14900"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisiones" sheetId="4" r:id="R27869f7de55d456c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios" sheetId="5" r:id="R7344411dc8034956"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product_Backlog" sheetId="1" r:id="Re9a27dff042841d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint_Backlogs" sheetId="2" r:id="Rb5fd55b52960495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAID" sheetId="3" r:id="R3795076e96e14777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisiones" sheetId="4" r:id="Rbd927d08b2c44d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios" sheetId="5" r:id="R43627eeaf9bf41e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -396,7 +396,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="19" t="str">
-        <x:v>Ejecución Fase 2 al 29/09/2026. Reparto vigente en endpoints.json. Revisión humana pendiente.</x:v>
+        <x:v>Integración local A/B/C al 20/10/2026. E18 note y Stripe real pendientes.</x:v>
       </x:c>
       <x:c r="B2" s="19"/>
       <x:c r="C2" s="19"/>
@@ -513,7 +513,7 @@
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="J6" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -545,7 +545,7 @@
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -577,7 +577,7 @@
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="J8" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -769,7 +769,7 @@
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="J14" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PARCIAL / NOTE_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
@@ -801,7 +801,7 @@
         <x:v>Catalina</x:v>
       </x:c>
       <x:c r="J15" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
@@ -833,7 +833,7 @@
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>PROBADO_LOCAL / REVISION_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
@@ -865,7 +865,7 @@
         <x:v>Felipe</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>PLANIFICADO</x:v>
+        <x:v>STRIPE_REAL_PENDIENTE</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
@@ -1113,7 +1113,7 @@
         <x:v>Equipo A / B / C</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>A probado local; sprint grupal no aceptado</x:v>
+        <x:v>A/B/C probados local; revisión y aceptación pendientes</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
@@ -1136,7 +1136,7 @@
         <x:v>Equipo A / B / C</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>A probado local; sprint grupal no aceptado</x:v>
+        <x:v>A/B/C probados local; revisión y aceptación pendientes</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -1159,7 +1159,7 @@
         <x:v>Equipo A / B / C</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>A probado local; sprint grupal no aceptado</x:v>
+        <x:v>A/B/C probados local; revisión y aceptación pendientes</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -1182,7 +1182,7 @@
         <x:v>Equipo A / B / C</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>A probado local; sprint grupal no aceptado</x:v>
+        <x:v>A/B/C probados local; revisión y aceptación pendientes</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
@@ -1205,7 +1205,7 @@
         <x:v>Equipo A / B / C</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>A probado local; sprint grupal no aceptado</x:v>
+        <x:v>A/B/C probados local; revisión y aceptación pendientes</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
@@ -1329,13 +1329,13 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F5" s="12" t="str">
-        <x:v>23 pruebas de integración A y 5 unitarias verdes; 7 defectos B/C abiertos.</x:v>
+        <x:v>Regresión A/B/C y contrato 8/8. E18 note reproducido 400; Stripe real pendiente.</x:v>
       </x:c>
       <x:c r="G5" s="12" t="str">
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>ABIERTO_B_C</x:v>
+        <x:v>PENDIENTES_PUNTUALES</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -1389,13 +1389,13 @@
         <x:v>Alta</x:v>
       </x:c>
       <x:c r="F7" s="12" t="str">
-        <x:v>Rama equipo-a/backend-sprints desde c0bd41f; push pendiente.</x:v>
+        <x:v>A/B/C descargados de GitHub; rama local codex/integracion-fase2 en db6c916.</x:v>
       </x:c>
       <x:c r="G7" s="12" t="str">
         <x:v>Tsung-Hao</x:v>
       </x:c>
       <x:c r="H7" s="16" t="str">
-        <x:v>LOCAL_PREPARADO</x:v>
+        <x:v>INTEGRADO_LOCAL</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
@@ -1474,10 +1474,8 @@
       <x:c r="E10" s="15" t="str">
         <x:v>Media</x:v>
       </x:c>
-      <x:c r="F10" s="15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Trazar el código entregado al contrato antes de aceptar cada incremento.</x:t>
-        </x:is>
+      <x:c r="F10" s="15" t="str">
+        <x:v>E18 no admite note del contrato. Añadir validación y persistencia transaccional.</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
         <x:v>Catalina / Felipe</x:v>
